--- a/aglie-stuff/Team02-User Stories.xlsx
+++ b/aglie-stuff/Team02-User Stories.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emanuel Vochitoiu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livemdxac-my.sharepoint.com/personal/ev205_live_mdx_ac_uk/Documents/Documents/__Projects/Bloome-PortfolioManagement/aglie-stuff/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445158E9-0798-4C1C-AB9D-FBE01293B0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{445158E9-0798-4C1C-AB9D-FBE01293B0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4482D3CD-B0D4-4884-BC62-14BFF3DF6EFD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -248,7 +248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,8 +266,13 @@
       <sz val="9"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,11 +296,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE1F5EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -332,6 +332,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1EFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -362,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -373,38 +385,56 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -740,42 +770,42 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -789,33 +819,33 @@
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="15" t="s">
         <v>23</v>
       </c>
     </row>
@@ -829,73 +859,73 @@
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="20" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -906,36 +936,36 @@
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>44</v>
       </c>
     </row>
@@ -946,36 +976,36 @@
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>50</v>
       </c>
     </row>
@@ -986,36 +1016,36 @@
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>58</v>
       </c>
     </row>
